--- a/test/fixtures/many-sheets.xlsx
+++ b/test/fixtures/many-sheets.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Summary</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figures before March 2025 come from the old billing system and were converted at the average monthly exchange rate; later months use the rate on the invoice date. Forecast sheets assume the pricing approved in the Q4 2025 review.</t>
   </si>
 </sst>
 </file>
@@ -1553,6 +1556,11 @@
         <v>323</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
